--- a/docs/test/unit/NOUS-102/観点表_gate_candidates_rng.xlsx
+++ b/docs/test/unit/NOUS-102/観点表_gate_candidates_rng.xlsx
@@ -3671,7 +3671,7 @@
       <c r="Q47" s="7" t="inlineStr">
         <is>
           <t>既存テスト：一部 TC-NOUS61_DEV-16（available が空のときだけ）
-設計書は available が空のときだけ ['post'] と書く。重みがすべて 0 のときは記載なし（実装の値）。issues の確認事項 1</t>
+重みがすべて 0 のときも ['post'] を返すのを仕様とする（2026-10-23 NOUS-102 で Kouhei Tajima が決定。設計書への追記は別に起票）</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>apps/server/src/generation/gate.test.ts・candidates.test.ts（実装時、NOUS-61）, apps/server/src/generation/rng.test.ts（実装時、NOUS-48）, apps/server/src/generation/gate.ut.test.ts・candidates.ut.test.ts・rng.ut.test.ts（単体テストで追加）</t>
+          <t>apps/server/src/generation/gate.test.ts（実装時、NOUS-61）, apps/server/src/generation/candidates.test.ts（実装時、NOUS-61）, apps/server/src/generation/rng.test.ts（実装時、NOUS-48）, apps/server/src/generation/gate.ut.test.ts（単体テストで追加）, apps/server/src/generation/candidates.ut.test.ts（単体テストで追加）, apps/server/src/generation/rng.ut.test.ts（単体テストで追加）</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 1：重みがすべて 0（または選べる種類の重みがすべて 0）のとき、drawCandidates は post の重みが 0 でも ['post'] を返す（TC-UT_CAND-014）。設計書は「available が空なら ['post']」だけを定めている。設定の検証で弾くか、この動きでよいかを確認したい。</t>
+          <t>・確認事項 1（決定済み）：重みがすべて 0（または選べる種類の重みがすべて 0）のとき、drawCandidates は post の重みが 0 でも ['post'] を返す（TC-UT_CAND-014）。2026-10-23、NOUS-102 で Kouhei Tajima がこの動きを仕様と決めた。設計書 generation.md への追記は、ケース作成の終わりにまとめて起票される。</t>
         </is>
       </c>
     </row>
